--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/27.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/27.xlsx
@@ -426,13 +426,13 @@
         <v>-13.46539912520359</v>
       </c>
       <c r="E2">
-        <v>-12.43302703106767</v>
+        <v>-9.605915316200258</v>
       </c>
       <c r="F2">
-        <v>3.576087610027445</v>
+        <v>3.622635231125555</v>
       </c>
       <c r="G2">
-        <v>-15.37283116721573</v>
+        <v>-15.36362829253206</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.3743460056676</v>
       </c>
       <c r="E3">
-        <v>-12.18087311190335</v>
+        <v>-10.0179055732006</v>
       </c>
       <c r="F3">
-        <v>3.498560704799439</v>
+        <v>3.577422938280757</v>
       </c>
       <c r="G3">
-        <v>-15.67114006568552</v>
+        <v>-14.28557744464053</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.23442437998539</v>
       </c>
       <c r="E4">
-        <v>-13.16945785034097</v>
+        <v>-9.871920195132876</v>
       </c>
       <c r="F4">
-        <v>3.307459658443204</v>
+        <v>3.704622066450233</v>
       </c>
       <c r="G4">
-        <v>-14.87924118407526</v>
+        <v>-13.98696569979818</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.02655860891326</v>
       </c>
       <c r="E5">
-        <v>-13.65359354126491</v>
+        <v>-11.30202452309036</v>
       </c>
       <c r="F5">
-        <v>4.141246240791824</v>
+        <v>4.149770141366631</v>
       </c>
       <c r="G5">
-        <v>-14.44462269975886</v>
+        <v>-14.11276312254868</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.7836107544668</v>
       </c>
       <c r="E6">
-        <v>-15.18256921802126</v>
+        <v>-11.91935370120155</v>
       </c>
       <c r="F6">
-        <v>3.68966340789048</v>
+        <v>3.896667451645659</v>
       </c>
       <c r="G6">
-        <v>-14.51375913264843</v>
+        <v>-12.52759080230095</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.50616446577451</v>
       </c>
       <c r="E7">
-        <v>-15.3876215675507</v>
+        <v>-12.63627688688213</v>
       </c>
       <c r="F7">
-        <v>3.316985883575398</v>
+        <v>4.270421853584379</v>
       </c>
       <c r="G7">
-        <v>-14.05489074719747</v>
+        <v>-12.35583383176849</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.23760102635515</v>
       </c>
       <c r="E8">
-        <v>-15.23448020637029</v>
+        <v>-13.5513871637722</v>
       </c>
       <c r="F8">
-        <v>3.825010357833891</v>
+        <v>4.480782442055703</v>
       </c>
       <c r="G8">
-        <v>-13.00148271750147</v>
+        <v>-11.45413355951749</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.98060257060026</v>
       </c>
       <c r="E9">
-        <v>-15.64189362449067</v>
+        <v>-14.35088865022434</v>
       </c>
       <c r="F9">
-        <v>4.458245878495139</v>
+        <v>4.383712693060851</v>
       </c>
       <c r="G9">
-        <v>-13.79268975179508</v>
+        <v>-11.59760050166064</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.77463839755253</v>
       </c>
       <c r="E10">
-        <v>-16.73461598368704</v>
+        <v>-15.40074571533715</v>
       </c>
       <c r="F10">
-        <v>4.567819005067847</v>
+        <v>4.373038350708376</v>
       </c>
       <c r="G10">
-        <v>-13.35837541922354</v>
+        <v>-11.26343302623191</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.61539049882186</v>
       </c>
       <c r="E11">
-        <v>-16.61062185958428</v>
+        <v>-15.06002041145954</v>
       </c>
       <c r="F11">
-        <v>4.22149847477504</v>
+        <v>4.749701978965728</v>
       </c>
       <c r="G11">
-        <v>-12.86298141157061</v>
+        <v>-11.00851339749413</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.53292029250594</v>
       </c>
       <c r="E12">
-        <v>-18.23496357478135</v>
+        <v>-15.26079080011308</v>
       </c>
       <c r="F12">
-        <v>4.839061284175322</v>
+        <v>4.960869397287379</v>
       </c>
       <c r="G12">
-        <v>-11.15992483542805</v>
+        <v>-10.11346921857817</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.51151182572338</v>
       </c>
       <c r="E13">
-        <v>-19.49223201345609</v>
+        <v>-17.06777413653081</v>
       </c>
       <c r="F13">
-        <v>5.709325853473621</v>
+        <v>4.979603754469092</v>
       </c>
       <c r="G13">
-        <v>-11.41368790431196</v>
+        <v>-10.09040329011569</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.56519650556637</v>
       </c>
       <c r="E14">
-        <v>-18.31561063228687</v>
+        <v>-16.86850305716553</v>
       </c>
       <c r="F14">
-        <v>4.671613440638625</v>
+        <v>5.005357697022129</v>
       </c>
       <c r="G14">
-        <v>-11.3220155241119</v>
+        <v>-9.385698056359436</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.66028965128104</v>
       </c>
       <c r="E15">
-        <v>-19.60788233600727</v>
+        <v>-18.45153693252585</v>
       </c>
       <c r="F15">
-        <v>5.343059892856209</v>
+        <v>5.754534832848807</v>
       </c>
       <c r="G15">
-        <v>-11.34232320091388</v>
+        <v>-9.425775596577616</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.78827660411018</v>
       </c>
       <c r="E16">
-        <v>-21.96298989023057</v>
+        <v>-18.78136836309844</v>
       </c>
       <c r="F16">
-        <v>5.451683710385308</v>
+        <v>5.972060799354346</v>
       </c>
       <c r="G16">
-        <v>-10.69035370252582</v>
+        <v>-8.671810833876236</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.89978127934206</v>
       </c>
       <c r="E17">
-        <v>-21.10436328735817</v>
+        <v>-19.38318114370007</v>
       </c>
       <c r="F17">
-        <v>6.097134336768238</v>
+        <v>6.073086831064968</v>
       </c>
       <c r="G17">
-        <v>-10.20228413882326</v>
+        <v>-8.760149293233441</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.97570938173866</v>
       </c>
       <c r="E18">
-        <v>-21.9239870826791</v>
+        <v>-20.18066832265967</v>
       </c>
       <c r="F18">
-        <v>5.657050900152556</v>
+        <v>6.371030705034283</v>
       </c>
       <c r="G18">
-        <v>-9.750784579980717</v>
+        <v>-7.875589864595393</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.97104486916787</v>
       </c>
       <c r="E19">
-        <v>-23.28564648800341</v>
+        <v>-21.50633599864302</v>
       </c>
       <c r="F19">
-        <v>5.965244992364112</v>
+        <v>6.453668637137562</v>
       </c>
       <c r="G19">
-        <v>-9.871425782163767</v>
+        <v>-7.833924991665816</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.8789679895034</v>
       </c>
       <c r="E20">
-        <v>-24.46797022832163</v>
+        <v>-22.17185073454487</v>
       </c>
       <c r="F20">
-        <v>6.54866912436022</v>
+        <v>6.49799954706578</v>
       </c>
       <c r="G20">
-        <v>-9.13474023253867</v>
+        <v>-7.541609057404931</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.67945876680213</v>
       </c>
       <c r="E21">
-        <v>-23.49311185331257</v>
+        <v>-22.64922915064331</v>
       </c>
       <c r="F21">
-        <v>6.548614452111636</v>
+        <v>6.472991135175263</v>
       </c>
       <c r="G21">
-        <v>-9.494342887146319</v>
+        <v>-7.481574985532281</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.39213208065195</v>
       </c>
       <c r="E22">
-        <v>-23.01171728186302</v>
+        <v>-22.23656192019702</v>
       </c>
       <c r="F22">
-        <v>6.670086248058155</v>
+        <v>6.738529276347061</v>
       </c>
       <c r="G22">
-        <v>-8.769606715514749</v>
+        <v>-7.24802821738965</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.02384394145382</v>
       </c>
       <c r="E23">
-        <v>-24.58001556344285</v>
+        <v>-23.64928921197142</v>
       </c>
       <c r="F23">
-        <v>7.414639437042407</v>
+        <v>7.01467549047911</v>
       </c>
       <c r="G23">
-        <v>-8.309263259369812</v>
+        <v>-6.723025755328907</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.61101364198491</v>
       </c>
       <c r="E24">
-        <v>-25.92168140944944</v>
+        <v>-24.14953105641305</v>
       </c>
       <c r="F24">
-        <v>6.928200560566064</v>
+        <v>7.028966484912207</v>
       </c>
       <c r="G24">
-        <v>-7.841211579819613</v>
+        <v>-6.396231022625483</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.16942269330281</v>
       </c>
       <c r="E25">
-        <v>-26.77468871739935</v>
+        <v>-24.72537795981185</v>
       </c>
       <c r="F25">
-        <v>6.630100953525023</v>
+        <v>6.91816240437894</v>
       </c>
       <c r="G25">
-        <v>-8.408778316321573</v>
+        <v>-5.919091341153619</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.734395214772809</v>
       </c>
       <c r="E26">
-        <v>-25.41546309391139</v>
+        <v>-25.32107306013201</v>
       </c>
       <c r="F26">
-        <v>7.809754120829715</v>
+        <v>6.866790371526926</v>
       </c>
       <c r="G26">
-        <v>-8.441412623710489</v>
+        <v>-5.974619267862008</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.316144946663954</v>
       </c>
       <c r="E27">
-        <v>-23.79859300588769</v>
+        <v>-24.62321726764372</v>
       </c>
       <c r="F27">
-        <v>6.733862254399689</v>
+        <v>7.318018663179872</v>
       </c>
       <c r="G27">
-        <v>-8.413319706537814</v>
+        <v>-5.99681059688647</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.939429109651433</v>
       </c>
       <c r="E28">
-        <v>-26.83700350011708</v>
+        <v>-25.47415212314254</v>
       </c>
       <c r="F28">
-        <v>6.464728998699741</v>
+        <v>6.60287748719942</v>
       </c>
       <c r="G28">
-        <v>-7.586678341281319</v>
+        <v>-5.305965806164437</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.604035496362222</v>
       </c>
       <c r="E29">
-        <v>-26.38638007137318</v>
+        <v>-26.41420243403821</v>
       </c>
       <c r="F29">
-        <v>6.620861343514197</v>
+        <v>6.779790256680505</v>
       </c>
       <c r="G29">
-        <v>-7.288238905581977</v>
+        <v>-5.628155185409137</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.323449441201175</v>
       </c>
       <c r="E30">
-        <v>-26.92320755437522</v>
+        <v>-25.08256244016976</v>
       </c>
       <c r="F30">
-        <v>6.373197714160007</v>
+        <v>6.609655189289126</v>
       </c>
       <c r="G30">
-        <v>-7.412126568664076</v>
+        <v>-5.882470426774073</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.089575336362897</v>
       </c>
       <c r="E31">
-        <v>-26.482834251181</v>
+        <v>-26.98591273895748</v>
       </c>
       <c r="F31">
-        <v>7.075444523148482</v>
+        <v>6.384097372446043</v>
       </c>
       <c r="G31">
-        <v>-7.568802573065966</v>
+        <v>-5.32058336513008</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.909740411065709</v>
       </c>
       <c r="E32">
-        <v>-26.17496084888278</v>
+        <v>-25.74061800853221</v>
       </c>
       <c r="F32">
-        <v>6.481143927153616</v>
+        <v>6.115925022933342</v>
       </c>
       <c r="G32">
-        <v>-7.513906446548627</v>
+        <v>-5.540366287788361</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.774557649731726</v>
       </c>
       <c r="E33">
-        <v>-26.71403106600023</v>
+        <v>-26.6752026933244</v>
       </c>
       <c r="F33">
-        <v>7.291963194892217</v>
+        <v>6.401976854468067</v>
       </c>
       <c r="G33">
-        <v>-6.225919099224208</v>
+        <v>-6.106258231635121</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.690493097696203</v>
       </c>
       <c r="E34">
-        <v>-26.97632712721978</v>
+        <v>-25.99109818353262</v>
       </c>
       <c r="F34">
-        <v>6.27888145841206</v>
+        <v>6.343727715438011</v>
       </c>
       <c r="G34">
-        <v>-7.239344880879607</v>
+        <v>-5.491490538298129</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.649008658471906</v>
       </c>
       <c r="E35">
-        <v>-26.41752915630939</v>
+        <v>-26.26720782561855</v>
       </c>
       <c r="F35">
-        <v>6.082309873727738</v>
+        <v>6.729133933264509</v>
       </c>
       <c r="G35">
-        <v>-7.004492740441421</v>
+        <v>-5.301616305675642</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.654282348433853</v>
       </c>
       <c r="E36">
-        <v>-26.72089217110884</v>
+        <v>-24.98486645017582</v>
       </c>
       <c r="F36">
-        <v>6.251727574948292</v>
+        <v>6.787099770642808</v>
       </c>
       <c r="G36">
-        <v>-7.299491214769676</v>
+        <v>-5.074831366023996</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.696025824256544</v>
       </c>
       <c r="E37">
-        <v>-25.43853418282081</v>
+        <v>-25.0960188448622</v>
       </c>
       <c r="F37">
-        <v>6.251020149186302</v>
+        <v>6.545009397174652</v>
       </c>
       <c r="G37">
-        <v>-8.072819870103341</v>
+        <v>-5.519793620410389</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.77442084146892</v>
       </c>
       <c r="E38">
-        <v>-26.33792040163508</v>
+        <v>-25.48836856550743</v>
       </c>
       <c r="F38">
-        <v>6.488211557834301</v>
+        <v>6.550256276303984</v>
       </c>
       <c r="G38">
-        <v>-7.695304896856065</v>
+        <v>-5.555268417914436</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.877511486498729</v>
       </c>
       <c r="E39">
-        <v>-25.85197391057352</v>
+        <v>-26.27534396660389</v>
       </c>
       <c r="F39">
-        <v>6.996226091683959</v>
+        <v>7.092076483861891</v>
       </c>
       <c r="G39">
-        <v>-7.546545975426725</v>
+        <v>-5.259828727750283</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.002798896759876</v>
       </c>
       <c r="E40">
-        <v>-26.51864739243499</v>
+        <v>-24.41730105015872</v>
       </c>
       <c r="F40">
-        <v>6.68975003346581</v>
+        <v>6.919784347753621</v>
       </c>
       <c r="G40">
-        <v>-7.991292843384351</v>
+        <v>-4.788380469487046</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.138357059491833</v>
       </c>
       <c r="E41">
-        <v>-24.63732987972548</v>
+        <v>-24.61948768387402</v>
       </c>
       <c r="F41">
-        <v>6.639913793778586</v>
+        <v>7.069190349257346</v>
       </c>
       <c r="G41">
-        <v>-8.404856977945721</v>
+        <v>-5.297428671351497</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.280806587356064</v>
       </c>
       <c r="E42">
-        <v>-23.83953536312785</v>
+        <v>-24.59705618950862</v>
       </c>
       <c r="F42">
-        <v>7.576290365494313</v>
+        <v>7.47750092577125</v>
       </c>
       <c r="G42">
-        <v>-6.785827216468136</v>
+        <v>-5.462281527812754</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.419583425867978</v>
       </c>
       <c r="E43">
-        <v>-25.46043406613663</v>
+        <v>-24.55835241317255</v>
       </c>
       <c r="F43">
-        <v>6.41961610994328</v>
+        <v>7.273715917743349</v>
       </c>
       <c r="G43">
-        <v>-7.787342781298877</v>
+        <v>-5.651884242997765</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.55171828124935</v>
       </c>
       <c r="E44">
-        <v>-22.89145274152996</v>
+        <v>-23.87832635690174</v>
       </c>
       <c r="F44">
-        <v>7.740853833734463</v>
+        <v>6.887734812939308</v>
       </c>
       <c r="G44">
-        <v>-7.321894014106019</v>
+        <v>-6.112074970584122</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.668627488703793</v>
       </c>
       <c r="E45">
-        <v>-24.35332913612239</v>
+        <v>-22.51211918517675</v>
       </c>
       <c r="F45">
-        <v>6.863799965202819</v>
+        <v>7.356189833100873</v>
       </c>
       <c r="G45">
-        <v>-8.112397452732324</v>
+        <v>-6.160107449571425</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.768005566923721</v>
       </c>
       <c r="E46">
-        <v>-25.22166594707224</v>
+        <v>-23.47904077334405</v>
       </c>
       <c r="F46">
-        <v>7.704251591674364</v>
+        <v>7.023383288617339</v>
       </c>
       <c r="G46">
-        <v>-8.757622092469243</v>
+        <v>-5.6559282863694</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.843680788471806</v>
       </c>
       <c r="E47">
-        <v>-23.81008909483481</v>
+        <v>-22.45350906696077</v>
       </c>
       <c r="F47">
-        <v>7.6274768440481</v>
+        <v>7.729662590122642</v>
       </c>
       <c r="G47">
-        <v>-8.953273902871864</v>
+        <v>-6.162169937798404</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.895496223068053</v>
       </c>
       <c r="E48">
-        <v>-23.59626100977601</v>
+        <v>-22.1467819509882</v>
       </c>
       <c r="F48">
-        <v>6.964648726289242</v>
+        <v>7.446622702464496</v>
       </c>
       <c r="G48">
-        <v>-8.493859871801364</v>
+        <v>-6.135459409886724</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.922022405300824</v>
       </c>
       <c r="E49">
-        <v>-22.19943636416438</v>
+        <v>-21.4346723372331</v>
       </c>
       <c r="F49">
-        <v>6.435830573485677</v>
+        <v>7.519401405739655</v>
       </c>
       <c r="G49">
-        <v>-8.417845432286509</v>
+        <v>-5.67030565683266</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.927070056728908</v>
       </c>
       <c r="E50">
-        <v>-22.46733926067245</v>
+        <v>-21.59396045117425</v>
       </c>
       <c r="F50">
-        <v>6.671431516720301</v>
+        <v>7.238487108837091</v>
       </c>
       <c r="G50">
-        <v>-8.611248086223886</v>
+        <v>-6.018769569642324</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.913528471547281</v>
       </c>
       <c r="E51">
-        <v>-22.04582153689295</v>
+        <v>-21.3667756384948</v>
       </c>
       <c r="F51">
-        <v>7.210165227335376</v>
+        <v>7.602387252152109</v>
       </c>
       <c r="G51">
-        <v>-8.587748774159275</v>
+        <v>-6.420957384647917</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.886703065681692</v>
       </c>
       <c r="E52">
-        <v>-20.98593446643068</v>
+        <v>-20.97006919916983</v>
       </c>
       <c r="F52">
-        <v>7.405389886622747</v>
+        <v>7.461597928372305</v>
       </c>
       <c r="G52">
-        <v>-8.71161685665694</v>
+        <v>-7.187310130434128</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.851393543367545</v>
       </c>
       <c r="E53">
-        <v>-21.82732939551637</v>
+        <v>-20.08330874278304</v>
       </c>
       <c r="F53">
-        <v>6.982415550344486</v>
+        <v>7.406062520953821</v>
       </c>
       <c r="G53">
-        <v>-9.467950870074755</v>
+        <v>-7.030809045919843</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.81308240262462</v>
       </c>
       <c r="E54">
-        <v>-21.60094199941129</v>
+        <v>-19.72526870089222</v>
       </c>
       <c r="F54">
-        <v>7.468610886804406</v>
+        <v>7.13199882247241</v>
       </c>
       <c r="G54">
-        <v>-8.418260540676496</v>
+        <v>-6.919573051126279</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.777888672645449</v>
       </c>
       <c r="E55">
-        <v>-20.92155969089584</v>
+        <v>-20.46363906985421</v>
       </c>
       <c r="F55">
-        <v>7.398022386942249</v>
+        <v>7.425093433665737</v>
       </c>
       <c r="G55">
-        <v>-8.235687255303057</v>
+        <v>-6.95341613326088</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.750990532033953</v>
       </c>
       <c r="E56">
-        <v>-19.79532091630811</v>
+        <v>-19.70230144226592</v>
       </c>
       <c r="F56">
-        <v>7.180425180840069</v>
+        <v>7.651015732166051</v>
       </c>
       <c r="G56">
-        <v>-9.424181737004741</v>
+        <v>-7.133938678758</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.738782698571736</v>
       </c>
       <c r="E57">
-        <v>-21.05687131585875</v>
+        <v>-19.37567213762478</v>
       </c>
       <c r="F57">
-        <v>7.060863600124405</v>
+        <v>7.45996604458879</v>
       </c>
       <c r="G57">
-        <v>-8.568023293401119</v>
+        <v>-7.594682884197672</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.744117511514773</v>
       </c>
       <c r="E58">
-        <v>-19.42720103053193</v>
+        <v>-18.72508404322436</v>
       </c>
       <c r="F58">
-        <v>7.697316499778127</v>
+        <v>7.404407442883027</v>
       </c>
       <c r="G58">
-        <v>-10.48723385722032</v>
+        <v>-7.665807399093372</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.771551386345878</v>
       </c>
       <c r="E59">
-        <v>-19.60251223376427</v>
+        <v>-18.86649258241212</v>
       </c>
       <c r="F59">
-        <v>6.975931090315371</v>
+        <v>7.70946699284239</v>
       </c>
       <c r="G59">
-        <v>-9.71888780793879</v>
+        <v>-7.290395380614236</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.819790760957073</v>
       </c>
       <c r="E60">
-        <v>-19.65268717977952</v>
+        <v>-18.10716926231637</v>
       </c>
       <c r="F60">
-        <v>6.97435056531083</v>
+        <v>7.522317258997509</v>
       </c>
       <c r="G60">
-        <v>-9.716015988888566</v>
+        <v>-7.980412565300887</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.890715493781924</v>
       </c>
       <c r="E61">
-        <v>-19.64544397922902</v>
+        <v>-16.8942405077455</v>
       </c>
       <c r="F61">
-        <v>7.593855067903274</v>
+        <v>7.615937686127103</v>
       </c>
       <c r="G61">
-        <v>-8.612740126757707</v>
+        <v>-8.045480152745203</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.979227703896832</v>
       </c>
       <c r="E62">
-        <v>-18.27776657069503</v>
+        <v>-17.48633892705835</v>
       </c>
       <c r="F62">
-        <v>7.437888396569377</v>
+        <v>7.522032300610946</v>
       </c>
       <c r="G62">
-        <v>-10.11972717336307</v>
+        <v>-7.739276362631891</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.085511254636762</v>
       </c>
       <c r="E63">
-        <v>-19.50492007405344</v>
+        <v>-17.45289726947083</v>
       </c>
       <c r="F63">
-        <v>6.923886423132284</v>
+        <v>7.54701917494899</v>
       </c>
       <c r="G63">
-        <v>-9.916162196104787</v>
+        <v>-7.638731366938936</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.202354871775972</v>
       </c>
       <c r="E64">
-        <v>-19.13850715813177</v>
+        <v>-16.52418522549195</v>
       </c>
       <c r="F64">
-        <v>6.904739538983977</v>
+        <v>7.609254417921317</v>
       </c>
       <c r="G64">
-        <v>-9.302239078643021</v>
+        <v>-8.039663413796204</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.330393010065418</v>
       </c>
       <c r="E65">
-        <v>-16.29822976336465</v>
+        <v>-16.85861841421244</v>
       </c>
       <c r="F65">
-        <v>7.131064424042052</v>
+        <v>7.787378260545295</v>
       </c>
       <c r="G65">
-        <v>-10.25559032188461</v>
+        <v>-8.199427929049381</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.461810169138356</v>
       </c>
       <c r="E66">
-        <v>-17.83825713545637</v>
+        <v>-16.28556246882393</v>
       </c>
       <c r="F66">
-        <v>6.915231640507835</v>
+        <v>7.3406927357293</v>
       </c>
       <c r="G66">
-        <v>-10.56049135044696</v>
+        <v>-8.928005811346774</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.597476591988721</v>
       </c>
       <c r="E67">
-        <v>-18.39149810961413</v>
+        <v>-16.60412208386092</v>
       </c>
       <c r="F67">
-        <v>7.330558488923451</v>
+        <v>7.757320120967312</v>
       </c>
       <c r="G67">
-        <v>-9.879391163911253</v>
+        <v>-8.498240701225251</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.728145710803291</v>
       </c>
       <c r="E68">
-        <v>-17.81304298950334</v>
+        <v>-15.85941391441724</v>
       </c>
       <c r="F68">
-        <v>6.981409912317488</v>
+        <v>7.45032881822462</v>
       </c>
       <c r="G68">
-        <v>-10.49891955001014</v>
+        <v>-8.23204657197075</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.854823394523374</v>
       </c>
       <c r="E69">
-        <v>-17.43240532479413</v>
+        <v>-16.74123620253881</v>
       </c>
       <c r="F69">
-        <v>7.065076676735043</v>
+        <v>7.728236141455021</v>
       </c>
       <c r="G69">
-        <v>-10.33745805077274</v>
+        <v>-8.627575682896708</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.967392032844096</v>
       </c>
       <c r="E70">
-        <v>-17.71395982692691</v>
+        <v>-16.04266190449133</v>
       </c>
       <c r="F70">
-        <v>7.022493622026732</v>
+        <v>7.744603024599534</v>
       </c>
       <c r="G70">
-        <v>-10.22476656586963</v>
+        <v>-8.087245539341538</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.06764647332675</v>
       </c>
       <c r="E71">
-        <v>-18.23443611694309</v>
+        <v>-16.51960423340066</v>
       </c>
       <c r="F71">
-        <v>6.945584678881215</v>
+        <v>7.652006459579799</v>
       </c>
       <c r="G71">
-        <v>-9.487031496918906</v>
+        <v>-8.485718264793977</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.14523112236184</v>
       </c>
       <c r="E72">
-        <v>-18.32657095697309</v>
+        <v>-16.30234559578756</v>
       </c>
       <c r="F72">
-        <v>7.584299021544579</v>
+        <v>7.092493981032901</v>
       </c>
       <c r="G72">
-        <v>-9.374658522855913</v>
+        <v>-8.54582804825977</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.20431774462428</v>
       </c>
       <c r="E73">
-        <v>-16.74259014943071</v>
+        <v>-15.51677813333021</v>
       </c>
       <c r="F73">
-        <v>6.975001662089431</v>
+        <v>7.205254665371581</v>
       </c>
       <c r="G73">
-        <v>-9.318973951472058</v>
+        <v>-8.221534408874632</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.23630931660055</v>
       </c>
       <c r="E74">
-        <v>-18.27434432456337</v>
+        <v>-16.10196976220988</v>
       </c>
       <c r="F74">
-        <v>6.455385014396162</v>
+        <v>7.373716430609305</v>
       </c>
       <c r="G74">
-        <v>-9.910922431710423</v>
+        <v>-8.067671481769667</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.2478976887129</v>
       </c>
       <c r="E75">
-        <v>-18.57786516139317</v>
+        <v>-15.90622475925938</v>
       </c>
       <c r="F75">
-        <v>6.629146674276998</v>
+        <v>7.312682320371038</v>
       </c>
       <c r="G75">
-        <v>-9.219769573126639</v>
+        <v>-8.338985281167341</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.23094926348306</v>
       </c>
       <c r="E76">
-        <v>-18.26668995609171</v>
+        <v>-16.77092335708869</v>
       </c>
       <c r="F76">
-        <v>6.812817265030121</v>
+        <v>7.266971350349755</v>
       </c>
       <c r="G76">
-        <v>-10.06085488283347</v>
+        <v>-7.941417178715724</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.19297696113593</v>
       </c>
       <c r="E77">
-        <v>-19.00688773803663</v>
+        <v>-16.96724565641333</v>
       </c>
       <c r="F77">
-        <v>6.624521070699766</v>
+        <v>7.452355004891868</v>
       </c>
       <c r="G77">
-        <v>-9.982736183178178</v>
+        <v>-8.186794535972984</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.12474487585072</v>
       </c>
       <c r="E78">
-        <v>-18.17578446661387</v>
+        <v>-17.84537573966713</v>
       </c>
       <c r="F78">
-        <v>6.217214475478055</v>
+        <v>7.495880741704565</v>
       </c>
       <c r="G78">
-        <v>-8.751639571238707</v>
+        <v>-7.574256418516802</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.03339238595483</v>
       </c>
       <c r="E79">
-        <v>-19.45170497734842</v>
+        <v>-17.82453492523914</v>
       </c>
       <c r="F79">
-        <v>6.099950785937756</v>
+        <v>7.529109871700465</v>
       </c>
       <c r="G79">
-        <v>-9.206091882213796</v>
+        <v>-7.817838888867672</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.908421261399136</v>
       </c>
       <c r="E80">
-        <v>-19.53618129569543</v>
+        <v>-18.04846777345125</v>
       </c>
       <c r="F80">
-        <v>7.090973098481362</v>
+        <v>7.24405539451871</v>
       </c>
       <c r="G80">
-        <v>-8.816648416929723</v>
+        <v>-7.437469066410013</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.756870311201624</v>
       </c>
       <c r="E81">
-        <v>-18.79475000998704</v>
+        <v>-18.74463736214166</v>
       </c>
       <c r="F81">
-        <v>6.328339962563608</v>
+        <v>7.360439357877235</v>
       </c>
       <c r="G81">
-        <v>-8.688383840540624</v>
+        <v>-7.187354513092178</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.568379104261208</v>
       </c>
       <c r="E82">
-        <v>-20.57779008311713</v>
+        <v>-18.70276053235341</v>
       </c>
       <c r="F82">
-        <v>7.158948927555089</v>
+        <v>7.250163775746953</v>
       </c>
       <c r="G82">
-        <v>-8.918369553060975</v>
+        <v>-7.26371618163765</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.352496821235722</v>
       </c>
       <c r="E83">
-        <v>-20.91920897328598</v>
+        <v>-19.37226235112709</v>
       </c>
       <c r="F83">
-        <v>6.279602138052496</v>
+        <v>7.114608077218037</v>
       </c>
       <c r="G83">
-        <v>-8.232130115797666</v>
+        <v>-6.576542097810722</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.101681761181441</v>
       </c>
       <c r="E84">
-        <v>-22.95531667207185</v>
+        <v>-20.55719846136863</v>
       </c>
       <c r="F84">
-        <v>6.793978533555655</v>
+        <v>7.113418541627617</v>
       </c>
       <c r="G84">
-        <v>-7.513802016764982</v>
+        <v>-6.441443897454383</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.829563560390534</v>
       </c>
       <c r="E85">
-        <v>-22.27931507757481</v>
+        <v>-21.27623563161354</v>
       </c>
       <c r="F85">
-        <v>6.997660824025608</v>
+        <v>7.013374953656715</v>
       </c>
       <c r="G85">
-        <v>-8.810968742071756</v>
+        <v>-6.912988753267491</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.53246037379796</v>
       </c>
       <c r="E86">
-        <v>-23.70493393730148</v>
+        <v>-22.23434825856089</v>
       </c>
       <c r="F86">
-        <v>6.707682531001613</v>
+        <v>7.087994289300894</v>
       </c>
       <c r="G86">
-        <v>-8.270991049036386</v>
+        <v>-6.658347168828666</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.227711869646425</v>
       </c>
       <c r="E87">
-        <v>-24.59129983861241</v>
+        <v>-23.11600441822947</v>
       </c>
       <c r="F87">
-        <v>6.381970124955654</v>
+        <v>7.112759161174989</v>
       </c>
       <c r="G87">
-        <v>-8.902509279669962</v>
+        <v>-6.755200571669786</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.913131113192094</v>
       </c>
       <c r="E88">
-        <v>-26.36904872051467</v>
+        <v>-25.26343479336604</v>
       </c>
       <c r="F88">
-        <v>6.598347974240912</v>
+        <v>7.641931855226952</v>
       </c>
       <c r="G88">
-        <v>-7.660024599824056</v>
+        <v>-6.678016518578113</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.605629616051327</v>
       </c>
       <c r="E89">
-        <v>-27.46654311952326</v>
+        <v>-26.11871390791063</v>
       </c>
       <c r="F89">
-        <v>6.873631029539244</v>
+        <v>7.557551038108183</v>
       </c>
       <c r="G89">
-        <v>-7.765992112032753</v>
+        <v>-5.889890162902017</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.300391513602237</v>
       </c>
       <c r="E90">
-        <v>-30.86293343407926</v>
+        <v>-28.02583116936997</v>
       </c>
       <c r="F90">
-        <v>6.866197260466521</v>
+        <v>7.219391583467758</v>
       </c>
       <c r="G90">
-        <v>-6.966506406640723</v>
+        <v>-5.501703771138565</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.011423810816255</v>
       </c>
       <c r="E91">
-        <v>-30.78777069212818</v>
+        <v>-29.05696140461913</v>
       </c>
       <c r="F91">
-        <v>6.612264546607943</v>
+        <v>7.404861388219762</v>
       </c>
       <c r="G91">
-        <v>-7.681158577289118</v>
+        <v>-5.717335609896975</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.730098721656112</v>
       </c>
       <c r="E92">
-        <v>-32.99476227087411</v>
+        <v>-30.14328158855827</v>
       </c>
       <c r="F92">
-        <v>6.078892029823787</v>
+        <v>7.16505068184411</v>
       </c>
       <c r="G92">
-        <v>-6.930621722235871</v>
+        <v>-6.309700503897624</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.466915294155915</v>
       </c>
       <c r="E93">
-        <v>-36.00725672643657</v>
+        <v>-32.77551009182509</v>
       </c>
       <c r="F93">
-        <v>6.197388330059451</v>
+        <v>6.844447645938617</v>
       </c>
       <c r="G93">
-        <v>-7.542167756747428</v>
+        <v>-6.666868639174059</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.21084369397386</v>
       </c>
       <c r="E94">
-        <v>-37.01659713847002</v>
+        <v>-34.50360733233902</v>
       </c>
       <c r="F94">
-        <v>6.27023827293125</v>
+        <v>7.11019122222631</v>
       </c>
       <c r="G94">
-        <v>-8.290375827625404</v>
+        <v>-6.129861973483377</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.971362397634844</v>
       </c>
       <c r="E95">
-        <v>-38.37092404920034</v>
+        <v>-37.49608330931581</v>
       </c>
       <c r="F95">
-        <v>5.938695817104388</v>
+        <v>7.000840098117552</v>
       </c>
       <c r="G95">
-        <v>-7.391783646810121</v>
+        <v>-5.811533885488934</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.739368470207951</v>
       </c>
       <c r="E96">
-        <v>-41.6680713025439</v>
+        <v>-38.46874878874535</v>
       </c>
       <c r="F96">
-        <v>5.499366194825253</v>
+        <v>6.791910928518267</v>
       </c>
       <c r="G96">
-        <v>-7.620303426242563</v>
+        <v>-5.801396364241641</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.525746044738294</v>
       </c>
       <c r="E97">
-        <v>-41.61640535366303</v>
+        <v>-41.62317924133383</v>
       </c>
       <c r="F97">
-        <v>5.41738101623538</v>
+        <v>6.442088060846425</v>
       </c>
       <c r="G97">
-        <v>-7.085235238410782</v>
+        <v>-6.050142887393733</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.327306125771761</v>
       </c>
       <c r="E98">
-        <v>-44.84843233003894</v>
+        <v>-43.91179803545795</v>
       </c>
       <c r="F98">
-        <v>5.290571220745221</v>
+        <v>6.526558341644696</v>
       </c>
       <c r="G98">
-        <v>-5.79276524262342</v>
+        <v>-6.469266602561877</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.156630207191386</v>
       </c>
       <c r="E99">
-        <v>-48.78356164310923</v>
+        <v>-45.63383781725462</v>
       </c>
       <c r="F99">
-        <v>4.99237717982026</v>
+        <v>6.474626332428389</v>
       </c>
       <c r="G99">
-        <v>-9.488425634530561</v>
+        <v>-6.323302483217325</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.017812201914735</v>
       </c>
       <c r="E100">
-        <v>-48.90271623771573</v>
+        <v>-48.5016624244365</v>
       </c>
       <c r="F100">
-        <v>4.856914258440457</v>
+        <v>5.873516556382511</v>
       </c>
       <c r="G100">
-        <v>-7.083183193162166</v>
+        <v>-6.078821916727112</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.919689825977819</v>
       </c>
       <c r="E101">
-        <v>-51.74088483943267</v>
+        <v>-50.97851410052732</v>
       </c>
       <c r="F101">
-        <v>4.732006394507125</v>
+        <v>5.8093329932788</v>
       </c>
       <c r="G101">
-        <v>-7.648881941909184</v>
+        <v>-6.114014753815319</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.875961335987449</v>
       </c>
       <c r="E102">
-        <v>-54.27663320532089</v>
+        <v>-52.70869313821782</v>
       </c>
       <c r="F102">
-        <v>3.66988862125085</v>
+        <v>5.576974280058733</v>
       </c>
       <c r="G102">
-        <v>-6.877485237572942</v>
+        <v>-5.978350021882708</v>
       </c>
     </row>
   </sheetData>
